--- a/Opptaksområder/KLASS TSB/OPPTAK_TSB_2019.xlsx
+++ b/Opptaksområder/KLASS TSB/OPPTAK_TSB_2019.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="477">
   <si>
     <t xml:space="preserve">KOMMUNE</t>
   </si>
@@ -875,6 +875,15 @@
     <t xml:space="preserve">1444</t>
   </si>
   <si>
+    <t xml:space="preserve">1445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1502</t>
+  </si>
+  <si>
     <t xml:space="preserve">997005562</t>
   </si>
   <si>
@@ -887,15 +896,6 @@
     <t xml:space="preserve">HELSE MIDT-NORGE RHF</t>
   </si>
   <si>
-    <t xml:space="preserve">1445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1502</t>
-  </si>
-  <si>
     <t xml:space="preserve">1504</t>
   </si>
   <si>
@@ -992,312 +992,312 @@
     <t xml:space="preserve">1571</t>
   </si>
   <si>
+    <t xml:space="preserve">1573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">983974910</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NORDLANDSSYKEHUSET HF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">883658752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HELSE NORD RHF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">983974899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIVERSITETSSYKEHUSET NORD-NORGE HF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">983974929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HELGELANDSSYKEHUSET HF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1820</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1840</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1850</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1870</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1920</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1940</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">983974880</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FINNMARKSSYKEHUSET HF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5001</t>
+  </si>
+  <si>
     <t xml:space="preserve">883974832</t>
   </si>
   <si>
     <t xml:space="preserve">ST OLAVS HOSPITAL HF</t>
   </si>
   <si>
-    <t xml:space="preserve">1573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">983974910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NORDLANDSSYKEHUSET HF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">883658752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HELSE NORD RHF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">983974899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNIVERSITETSSYKEHUSET NORD-NORGE HF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">983974929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HELGELANDSSYKEHUSET HF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1820</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1840</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1850</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1860</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1870</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1920</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1940</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">983974880</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FINNMARKSSYKEHUSET HF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2030</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5001</t>
-  </si>
-  <si>
     <t xml:space="preserve">5004</t>
   </si>
   <si>
@@ -1443,9 +1443,6 @@
   </si>
   <si>
     <t xml:space="preserve">5061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4619</t>
   </si>
 </sst>
 </file>
@@ -5312,13 +5309,13 @@
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B209" t="s">
-        <v>227</v>
+        <v>202</v>
       </c>
       <c r="C209" t="s">
-        <v>228</v>
+        <v>203</v>
       </c>
       <c r="D209" t="s">
         <v>197</v>
@@ -5329,13 +5326,13 @@
     </row>
     <row r="210">
       <c r="A210" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B210" t="s">
-        <v>202</v>
+        <v>227</v>
       </c>
       <c r="C210" t="s">
-        <v>203</v>
+        <v>228</v>
       </c>
       <c r="D210" t="s">
         <v>197</v>
@@ -5346,7 +5343,7 @@
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B211" t="s">
         <v>227</v>
@@ -5363,7 +5360,7 @@
     </row>
     <row r="212">
       <c r="A212" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B212" t="s">
         <v>227</v>
@@ -5380,7 +5377,7 @@
     </row>
     <row r="213">
       <c r="A213" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B213" t="s">
         <v>227</v>
@@ -5397,7 +5394,7 @@
     </row>
     <row r="214">
       <c r="A214" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B214" t="s">
         <v>227</v>
@@ -5414,7 +5411,7 @@
     </row>
     <row r="215">
       <c r="A215" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B215" t="s">
         <v>227</v>
@@ -5431,7 +5428,7 @@
     </row>
     <row r="216">
       <c r="A216" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B216" t="s">
         <v>227</v>
@@ -5448,7 +5445,7 @@
     </row>
     <row r="217">
       <c r="A217" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B217" t="s">
         <v>227</v>
@@ -5465,7 +5462,7 @@
     </row>
     <row r="218">
       <c r="A218" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B218" t="s">
         <v>227</v>
@@ -5482,7 +5479,7 @@
     </row>
     <row r="219">
       <c r="A219" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B219" t="s">
         <v>227</v>
@@ -5499,7 +5496,7 @@
     </row>
     <row r="220">
       <c r="A220" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B220" t="s">
         <v>227</v>
@@ -5516,7 +5513,7 @@
     </row>
     <row r="221">
       <c r="A221" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B221" t="s">
         <v>227</v>
@@ -5533,7 +5530,7 @@
     </row>
     <row r="222">
       <c r="A222" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B222" t="s">
         <v>227</v>
@@ -5550,7 +5547,7 @@
     </row>
     <row r="223">
       <c r="A223" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B223" t="s">
         <v>227</v>
@@ -5567,7 +5564,7 @@
     </row>
     <row r="224">
       <c r="A224" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B224" t="s">
         <v>227</v>
@@ -5584,7 +5581,7 @@
     </row>
     <row r="225">
       <c r="A225" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B225" t="s">
         <v>227</v>
@@ -5601,7 +5598,7 @@
     </row>
     <row r="226">
       <c r="A226" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B226" t="s">
         <v>227</v>
@@ -5618,7 +5615,7 @@
     </row>
     <row r="227">
       <c r="A227" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B227" t="s">
         <v>227</v>
@@ -5635,7 +5632,7 @@
     </row>
     <row r="228">
       <c r="A228" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B228" t="s">
         <v>227</v>
@@ -5652,7 +5649,7 @@
     </row>
     <row r="229">
       <c r="A229" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B229" t="s">
         <v>227</v>
@@ -5669,7 +5666,7 @@
     </row>
     <row r="230">
       <c r="A230" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B230" t="s">
         <v>227</v>
@@ -5686,13 +5683,13 @@
     </row>
     <row r="231">
       <c r="A231" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B231" t="s">
-        <v>227</v>
+        <v>262</v>
       </c>
       <c r="C231" t="s">
-        <v>228</v>
+        <v>263</v>
       </c>
       <c r="D231" t="s">
         <v>197</v>
@@ -5703,13 +5700,13 @@
     </row>
     <row r="232">
       <c r="A232" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B232" t="s">
-        <v>262</v>
+        <v>227</v>
       </c>
       <c r="C232" t="s">
-        <v>263</v>
+        <v>228</v>
       </c>
       <c r="D232" t="s">
         <v>197</v>
@@ -5720,13 +5717,13 @@
     </row>
     <row r="233">
       <c r="A233" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B233" t="s">
-        <v>227</v>
+        <v>262</v>
       </c>
       <c r="C233" t="s">
-        <v>228</v>
+        <v>263</v>
       </c>
       <c r="D233" t="s">
         <v>197</v>
@@ -5737,7 +5734,7 @@
     </row>
     <row r="234">
       <c r="A234" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B234" t="s">
         <v>262</v>
@@ -5754,7 +5751,7 @@
     </row>
     <row r="235">
       <c r="A235" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B235" t="s">
         <v>262</v>
@@ -5771,7 +5768,7 @@
     </row>
     <row r="236">
       <c r="A236" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B236" t="s">
         <v>262</v>
@@ -5788,7 +5785,7 @@
     </row>
     <row r="237">
       <c r="A237" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B237" t="s">
         <v>262</v>
@@ -5805,7 +5802,7 @@
     </row>
     <row r="238">
       <c r="A238" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B238" t="s">
         <v>262</v>
@@ -5822,7 +5819,7 @@
     </row>
     <row r="239">
       <c r="A239" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B239" t="s">
         <v>262</v>
@@ -5839,7 +5836,7 @@
     </row>
     <row r="240">
       <c r="A240" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B240" t="s">
         <v>262</v>
@@ -5856,7 +5853,7 @@
     </row>
     <row r="241">
       <c r="A241" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B241" t="s">
         <v>262</v>
@@ -5873,7 +5870,7 @@
     </row>
     <row r="242">
       <c r="A242" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B242" t="s">
         <v>262</v>
@@ -5890,7 +5887,7 @@
     </row>
     <row r="243">
       <c r="A243" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B243" t="s">
         <v>262</v>
@@ -5907,7 +5904,7 @@
     </row>
     <row r="244">
       <c r="A244" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B244" t="s">
         <v>262</v>
@@ -5924,7 +5921,7 @@
     </row>
     <row r="245">
       <c r="A245" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B245" t="s">
         <v>262</v>
@@ -5941,7 +5938,7 @@
     </row>
     <row r="246">
       <c r="A246" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B246" t="s">
         <v>262</v>
@@ -5958,7 +5955,7 @@
     </row>
     <row r="247">
       <c r="A247" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B247" t="s">
         <v>262</v>
@@ -5975,7 +5972,7 @@
     </row>
     <row r="248">
       <c r="A248" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B248" t="s">
         <v>262</v>
@@ -5992,7 +5989,7 @@
     </row>
     <row r="249">
       <c r="A249" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B249" t="s">
         <v>262</v>
@@ -6009,7 +6006,7 @@
     </row>
     <row r="250">
       <c r="A250" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B250" t="s">
         <v>262</v>
@@ -6026,7 +6023,7 @@
     </row>
     <row r="251">
       <c r="A251" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B251" t="s">
         <v>262</v>
@@ -6043,7 +6040,7 @@
     </row>
     <row r="252">
       <c r="A252" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B252" t="s">
         <v>262</v>
@@ -6060,7 +6057,7 @@
     </row>
     <row r="253">
       <c r="A253" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B253" t="s">
         <v>262</v>
@@ -6077,7 +6074,7 @@
     </row>
     <row r="254">
       <c r="A254" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B254" t="s">
         <v>262</v>
@@ -6094,24 +6091,24 @@
     </row>
     <row r="255">
       <c r="A255" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B255" t="s">
-        <v>287</v>
+        <v>262</v>
       </c>
       <c r="C255" t="s">
-        <v>288</v>
+        <v>263</v>
       </c>
       <c r="D255" t="s">
-        <v>289</v>
+        <v>197</v>
       </c>
       <c r="E255" t="s">
-        <v>290</v>
+        <v>198</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B256" t="s">
         <v>262</v>
@@ -6128,2132 +6125,2132 @@
     </row>
     <row r="257">
       <c r="A257" t="s">
+        <v>289</v>
+      </c>
+      <c r="B257" t="s">
+        <v>290</v>
+      </c>
+      <c r="C257" t="s">
+        <v>291</v>
+      </c>
+      <c r="D257" t="s">
         <v>292</v>
       </c>
-      <c r="B257" t="s">
-        <v>262</v>
-      </c>
-      <c r="C257" t="s">
-        <v>263</v>
-      </c>
-      <c r="D257" t="s">
-        <v>197</v>
-      </c>
       <c r="E257" t="s">
-        <v>198</v>
+        <v>293</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="s">
+        <v>294</v>
+      </c>
+      <c r="B258" t="s">
+        <v>290</v>
+      </c>
+      <c r="C258" t="s">
+        <v>291</v>
+      </c>
+      <c r="D258" t="s">
+        <v>292</v>
+      </c>
+      <c r="E258" t="s">
         <v>293</v>
-      </c>
-      <c r="B258" t="s">
-        <v>287</v>
-      </c>
-      <c r="C258" t="s">
-        <v>288</v>
-      </c>
-      <c r="D258" t="s">
-        <v>289</v>
-      </c>
-      <c r="E258" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B259" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C259" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D259" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E259" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B260" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C260" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D260" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E260" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B261" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C261" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D261" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E261" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B262" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C262" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D262" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E262" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B263" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C263" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D263" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E263" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B264" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C264" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D264" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E264" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B265" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C265" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D265" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E265" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B266" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C266" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D266" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E266" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B267" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C267" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D267" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E267" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B268" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C268" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D268" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E268" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B269" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C269" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D269" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E269" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B270" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C270" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D270" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E270" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B271" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C271" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D271" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E271" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B272" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C272" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D272" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E272" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B273" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C273" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D273" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E273" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B274" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C274" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D274" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E274" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B275" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C275" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D275" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E275" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B276" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C276" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D276" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E276" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B277" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C277" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D277" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E277" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B278" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C278" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D278" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E278" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B279" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C279" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D279" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E279" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B280" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C280" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D280" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E280" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B281" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C281" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D281" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E281" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B282" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C282" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D282" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E282" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B283" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C283" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D283" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E283" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B284" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C284" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D284" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E284" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B285" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C285" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D285" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E285" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B286" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C286" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D286" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E286" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B287" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C287" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D287" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E287" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B288" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C288" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D288" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E288" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B289" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C289" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D289" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E289" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B290" t="s">
-        <v>326</v>
+        <v>290</v>
       </c>
       <c r="C290" t="s">
-        <v>327</v>
+        <v>291</v>
       </c>
       <c r="D290" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E290" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B291" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C291" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D291" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E291" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="s">
+        <v>328</v>
+      </c>
+      <c r="B292" t="s">
         <v>329</v>
       </c>
-      <c r="B292" t="s">
-        <v>287</v>
-      </c>
       <c r="C292" t="s">
-        <v>288</v>
+        <v>330</v>
       </c>
       <c r="D292" t="s">
-        <v>289</v>
+        <v>331</v>
       </c>
       <c r="E292" t="s">
-        <v>290</v>
+        <v>332</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B293" t="s">
+        <v>334</v>
+      </c>
+      <c r="C293" t="s">
+        <v>335</v>
+      </c>
+      <c r="D293" t="s">
         <v>331</v>
       </c>
-      <c r="C293" t="s">
+      <c r="E293" t="s">
         <v>332</v>
-      </c>
-      <c r="D293" t="s">
-        <v>333</v>
-      </c>
-      <c r="E293" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B294" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C294" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D294" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E294" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="s">
+        <v>339</v>
+      </c>
+      <c r="B295" t="s">
+        <v>337</v>
+      </c>
+      <c r="C295" t="s">
         <v>338</v>
       </c>
-      <c r="B295" t="s">
-        <v>339</v>
-      </c>
-      <c r="C295" t="s">
-        <v>340</v>
-      </c>
       <c r="D295" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E295" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B296" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C296" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D296" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E296" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B297" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C297" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D297" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E297" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B298" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C298" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D298" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E298" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B299" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C299" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D299" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E299" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B300" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C300" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D300" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E300" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B301" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C301" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D301" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E301" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B302" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C302" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D302" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E302" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B303" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C303" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D303" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E303" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B304" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C304" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D304" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E304" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B305" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C305" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D305" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E305" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B306" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C306" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D306" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E306" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B307" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C307" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D307" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E307" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B308" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C308" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D308" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E308" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B309" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C309" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D309" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E309" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B310" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C310" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D310" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E310" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B311" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C311" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D311" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E311" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B312" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="C312" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="D312" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E312" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B313" t="s">
+        <v>329</v>
+      </c>
+      <c r="C313" t="s">
+        <v>330</v>
+      </c>
+      <c r="D313" t="s">
         <v>331</v>
       </c>
-      <c r="C313" t="s">
+      <c r="E313" t="s">
         <v>332</v>
-      </c>
-      <c r="D313" t="s">
-        <v>333</v>
-      </c>
-      <c r="E313" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B314" t="s">
+        <v>329</v>
+      </c>
+      <c r="C314" t="s">
+        <v>330</v>
+      </c>
+      <c r="D314" t="s">
         <v>331</v>
       </c>
-      <c r="C314" t="s">
+      <c r="E314" t="s">
         <v>332</v>
-      </c>
-      <c r="D314" t="s">
-        <v>333</v>
-      </c>
-      <c r="E314" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B315" t="s">
+        <v>329</v>
+      </c>
+      <c r="C315" t="s">
+        <v>330</v>
+      </c>
+      <c r="D315" t="s">
         <v>331</v>
       </c>
-      <c r="C315" t="s">
+      <c r="E315" t="s">
         <v>332</v>
-      </c>
-      <c r="D315" t="s">
-        <v>333</v>
-      </c>
-      <c r="E315" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B316" t="s">
+        <v>329</v>
+      </c>
+      <c r="C316" t="s">
+        <v>330</v>
+      </c>
+      <c r="D316" t="s">
         <v>331</v>
       </c>
-      <c r="C316" t="s">
+      <c r="E316" t="s">
         <v>332</v>
-      </c>
-      <c r="D316" t="s">
-        <v>333</v>
-      </c>
-      <c r="E316" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B317" t="s">
+        <v>329</v>
+      </c>
+      <c r="C317" t="s">
+        <v>330</v>
+      </c>
+      <c r="D317" t="s">
         <v>331</v>
       </c>
-      <c r="C317" t="s">
+      <c r="E317" t="s">
         <v>332</v>
-      </c>
-      <c r="D317" t="s">
-        <v>333</v>
-      </c>
-      <c r="E317" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B318" t="s">
+        <v>329</v>
+      </c>
+      <c r="C318" t="s">
+        <v>330</v>
+      </c>
+      <c r="D318" t="s">
         <v>331</v>
       </c>
-      <c r="C318" t="s">
+      <c r="E318" t="s">
         <v>332</v>
-      </c>
-      <c r="D318" t="s">
-        <v>333</v>
-      </c>
-      <c r="E318" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B319" t="s">
+        <v>329</v>
+      </c>
+      <c r="C319" t="s">
+        <v>330</v>
+      </c>
+      <c r="D319" t="s">
         <v>331</v>
       </c>
-      <c r="C319" t="s">
+      <c r="E319" t="s">
         <v>332</v>
-      </c>
-      <c r="D319" t="s">
-        <v>333</v>
-      </c>
-      <c r="E319" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B320" t="s">
+        <v>334</v>
+      </c>
+      <c r="C320" t="s">
+        <v>335</v>
+      </c>
+      <c r="D320" t="s">
         <v>331</v>
       </c>
-      <c r="C320" t="s">
+      <c r="E320" t="s">
         <v>332</v>
-      </c>
-      <c r="D320" t="s">
-        <v>333</v>
-      </c>
-      <c r="E320" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B321" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="C321" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="D321" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E321" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B322" t="s">
+        <v>334</v>
+      </c>
+      <c r="C322" t="s">
+        <v>335</v>
+      </c>
+      <c r="D322" t="s">
         <v>331</v>
       </c>
-      <c r="C322" t="s">
+      <c r="E322" t="s">
         <v>332</v>
-      </c>
-      <c r="D322" t="s">
-        <v>333</v>
-      </c>
-      <c r="E322" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B323" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C323" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D323" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E323" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B324" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C324" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D324" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E324" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B325" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C325" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D325" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E325" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B326" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="C326" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="D326" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E326" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B327" t="s">
+        <v>329</v>
+      </c>
+      <c r="C327" t="s">
+        <v>330</v>
+      </c>
+      <c r="D327" t="s">
         <v>331</v>
       </c>
-      <c r="C327" t="s">
+      <c r="E327" t="s">
         <v>332</v>
-      </c>
-      <c r="D327" t="s">
-        <v>333</v>
-      </c>
-      <c r="E327" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B328" t="s">
+        <v>329</v>
+      </c>
+      <c r="C328" t="s">
+        <v>330</v>
+      </c>
+      <c r="D328" t="s">
         <v>331</v>
       </c>
-      <c r="C328" t="s">
+      <c r="E328" t="s">
         <v>332</v>
-      </c>
-      <c r="D328" t="s">
-        <v>333</v>
-      </c>
-      <c r="E328" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B329" t="s">
+        <v>329</v>
+      </c>
+      <c r="C329" t="s">
+        <v>330</v>
+      </c>
+      <c r="D329" t="s">
         <v>331</v>
       </c>
-      <c r="C329" t="s">
+      <c r="E329" t="s">
         <v>332</v>
-      </c>
-      <c r="D329" t="s">
-        <v>333</v>
-      </c>
-      <c r="E329" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B330" t="s">
+        <v>329</v>
+      </c>
+      <c r="C330" t="s">
+        <v>330</v>
+      </c>
+      <c r="D330" t="s">
         <v>331</v>
       </c>
-      <c r="C330" t="s">
+      <c r="E330" t="s">
         <v>332</v>
-      </c>
-      <c r="D330" t="s">
-        <v>333</v>
-      </c>
-      <c r="E330" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B331" t="s">
+        <v>329</v>
+      </c>
+      <c r="C331" t="s">
+        <v>330</v>
+      </c>
+      <c r="D331" t="s">
         <v>331</v>
       </c>
-      <c r="C331" t="s">
+      <c r="E331" t="s">
         <v>332</v>
-      </c>
-      <c r="D331" t="s">
-        <v>333</v>
-      </c>
-      <c r="E331" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B332" t="s">
+        <v>329</v>
+      </c>
+      <c r="C332" t="s">
+        <v>330</v>
+      </c>
+      <c r="D332" t="s">
         <v>331</v>
       </c>
-      <c r="C332" t="s">
+      <c r="E332" t="s">
         <v>332</v>
-      </c>
-      <c r="D332" t="s">
-        <v>333</v>
-      </c>
-      <c r="E332" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B333" t="s">
+        <v>329</v>
+      </c>
+      <c r="C333" t="s">
+        <v>330</v>
+      </c>
+      <c r="D333" t="s">
         <v>331</v>
       </c>
-      <c r="C333" t="s">
+      <c r="E333" t="s">
         <v>332</v>
-      </c>
-      <c r="D333" t="s">
-        <v>333</v>
-      </c>
-      <c r="E333" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B334" t="s">
+        <v>329</v>
+      </c>
+      <c r="C334" t="s">
+        <v>330</v>
+      </c>
+      <c r="D334" t="s">
         <v>331</v>
       </c>
-      <c r="C334" t="s">
+      <c r="E334" t="s">
         <v>332</v>
-      </c>
-      <c r="D334" t="s">
-        <v>333</v>
-      </c>
-      <c r="E334" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B335" t="s">
+        <v>329</v>
+      </c>
+      <c r="C335" t="s">
+        <v>330</v>
+      </c>
+      <c r="D335" t="s">
         <v>331</v>
       </c>
-      <c r="C335" t="s">
+      <c r="E335" t="s">
         <v>332</v>
-      </c>
-      <c r="D335" t="s">
-        <v>333</v>
-      </c>
-      <c r="E335" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B336" t="s">
+        <v>329</v>
+      </c>
+      <c r="C336" t="s">
+        <v>330</v>
+      </c>
+      <c r="D336" t="s">
         <v>331</v>
       </c>
-      <c r="C336" t="s">
+      <c r="E336" t="s">
         <v>332</v>
-      </c>
-      <c r="D336" t="s">
-        <v>333</v>
-      </c>
-      <c r="E336" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B337" t="s">
+        <v>334</v>
+      </c>
+      <c r="C337" t="s">
+        <v>335</v>
+      </c>
+      <c r="D337" t="s">
         <v>331</v>
       </c>
-      <c r="C337" t="s">
+      <c r="E337" t="s">
         <v>332</v>
-      </c>
-      <c r="D337" t="s">
-        <v>333</v>
-      </c>
-      <c r="E337" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B338" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C338" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D338" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E338" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B339" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C339" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D339" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E339" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B340" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C340" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D340" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E340" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B341" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C341" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D341" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E341" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B342" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C342" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D342" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E342" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B343" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C343" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D343" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E343" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B344" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C344" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D344" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E344" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B345" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C345" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D345" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E345" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B346" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C346" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D346" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E346" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B347" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C347" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D347" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E347" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B348" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C348" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D348" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E348" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B349" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C349" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D349" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E349" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B350" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C350" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D350" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E350" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B351" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C351" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D351" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E351" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B352" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C352" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D352" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E352" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B353" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C353" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D353" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E353" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B354" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C354" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D354" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E354" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B355" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C355" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D355" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E355" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B356" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C356" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D356" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E356" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B357" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C357" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D357" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E357" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B358" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C358" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D358" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E358" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B359" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C359" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D359" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E359" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B360" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C360" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D360" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E360" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="s">
+        <v>404</v>
+      </c>
+      <c r="B361" t="s">
         <v>405</v>
       </c>
-      <c r="B361" t="s">
-        <v>336</v>
-      </c>
       <c r="C361" t="s">
-        <v>337</v>
+        <v>406</v>
       </c>
       <c r="D361" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E361" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="s">
+        <v>407</v>
+      </c>
+      <c r="B362" t="s">
+        <v>405</v>
+      </c>
+      <c r="C362" t="s">
         <v>406</v>
       </c>
-      <c r="B362" t="s">
-        <v>407</v>
-      </c>
-      <c r="C362" t="s">
-        <v>408</v>
-      </c>
       <c r="D362" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E362" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B363" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C363" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D363" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E363" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B364" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C364" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D364" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E364" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B365" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C365" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D365" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E365" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B366" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C366" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D366" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E366" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B367" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C367" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D367" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E367" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B368" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C368" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D368" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E368" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B369" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C369" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D369" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E369" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B370" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C370" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D370" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E370" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B371" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C371" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D371" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E371" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B372" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C372" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D372" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E372" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B373" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C373" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D373" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E373" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B374" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C374" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D374" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E374" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B375" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C375" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D375" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E375" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B376" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C376" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D376" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E376" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B377" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C377" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D377" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E377" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B378" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C378" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D378" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E378" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B379" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C379" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D379" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E379" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="s">
+        <v>425</v>
+      </c>
+      <c r="B380" t="s">
         <v>426</v>
       </c>
-      <c r="B380" t="s">
-        <v>407</v>
-      </c>
       <c r="C380" t="s">
-        <v>408</v>
+        <v>427</v>
       </c>
       <c r="D380" t="s">
-        <v>333</v>
+        <v>292</v>
       </c>
       <c r="E380" t="s">
-        <v>334</v>
+        <v>293</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B381" t="s">
-        <v>326</v>
+        <v>429</v>
       </c>
       <c r="C381" t="s">
-        <v>327</v>
+        <v>430</v>
       </c>
       <c r="D381" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E381" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="B382" t="s">
         <v>429</v>
@@ -8262,423 +8259,423 @@
         <v>430</v>
       </c>
       <c r="D382" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E382" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B383" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C383" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D383" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E383" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B384" t="s">
-        <v>326</v>
+        <v>426</v>
       </c>
       <c r="C384" t="s">
-        <v>327</v>
+        <v>427</v>
       </c>
       <c r="D384" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E384" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B385" t="s">
-        <v>326</v>
+        <v>426</v>
       </c>
       <c r="C385" t="s">
-        <v>327</v>
+        <v>427</v>
       </c>
       <c r="D385" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E385" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B386" t="s">
-        <v>326</v>
+        <v>426</v>
       </c>
       <c r="C386" t="s">
-        <v>327</v>
+        <v>427</v>
       </c>
       <c r="D386" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E386" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B387" t="s">
-        <v>326</v>
+        <v>426</v>
       </c>
       <c r="C387" t="s">
-        <v>327</v>
+        <v>427</v>
       </c>
       <c r="D387" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E387" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B388" t="s">
-        <v>326</v>
+        <v>426</v>
       </c>
       <c r="C388" t="s">
-        <v>327</v>
+        <v>427</v>
       </c>
       <c r="D388" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E388" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B389" t="s">
-        <v>326</v>
+        <v>426</v>
       </c>
       <c r="C389" t="s">
-        <v>327</v>
+        <v>427</v>
       </c>
       <c r="D389" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E389" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B390" t="s">
-        <v>326</v>
+        <v>426</v>
       </c>
       <c r="C390" t="s">
-        <v>327</v>
+        <v>427</v>
       </c>
       <c r="D390" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E390" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B391" t="s">
-        <v>326</v>
+        <v>426</v>
       </c>
       <c r="C391" t="s">
-        <v>327</v>
+        <v>427</v>
       </c>
       <c r="D391" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E391" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B392" t="s">
-        <v>326</v>
+        <v>429</v>
       </c>
       <c r="C392" t="s">
-        <v>327</v>
+        <v>430</v>
       </c>
       <c r="D392" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E392" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B393" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C393" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D393" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E393" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B394" t="s">
-        <v>326</v>
+        <v>426</v>
       </c>
       <c r="C394" t="s">
-        <v>327</v>
+        <v>427</v>
       </c>
       <c r="D394" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E394" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B395" t="s">
-        <v>326</v>
+        <v>426</v>
       </c>
       <c r="C395" t="s">
-        <v>327</v>
+        <v>427</v>
       </c>
       <c r="D395" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E395" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B396" t="s">
-        <v>326</v>
+        <v>426</v>
       </c>
       <c r="C396" t="s">
-        <v>327</v>
+        <v>427</v>
       </c>
       <c r="D396" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E396" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B397" t="s">
-        <v>326</v>
+        <v>426</v>
       </c>
       <c r="C397" t="s">
-        <v>327</v>
+        <v>427</v>
       </c>
       <c r="D397" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E397" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B398" t="s">
-        <v>326</v>
+        <v>426</v>
       </c>
       <c r="C398" t="s">
-        <v>327</v>
+        <v>427</v>
       </c>
       <c r="D398" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E398" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B399" t="s">
-        <v>326</v>
+        <v>426</v>
       </c>
       <c r="C399" t="s">
-        <v>327</v>
+        <v>427</v>
       </c>
       <c r="D399" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E399" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B400" t="s">
-        <v>326</v>
+        <v>426</v>
       </c>
       <c r="C400" t="s">
-        <v>327</v>
+        <v>427</v>
       </c>
       <c r="D400" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E400" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B401" t="s">
-        <v>326</v>
+        <v>426</v>
       </c>
       <c r="C401" t="s">
-        <v>327</v>
+        <v>427</v>
       </c>
       <c r="D401" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E401" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B402" t="s">
-        <v>326</v>
+        <v>426</v>
       </c>
       <c r="C402" t="s">
-        <v>327</v>
+        <v>427</v>
       </c>
       <c r="D402" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E402" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B403" t="s">
-        <v>326</v>
+        <v>426</v>
       </c>
       <c r="C403" t="s">
-        <v>327</v>
+        <v>427</v>
       </c>
       <c r="D403" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E403" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B404" t="s">
-        <v>326</v>
+        <v>426</v>
       </c>
       <c r="C404" t="s">
-        <v>327</v>
+        <v>427</v>
       </c>
       <c r="D404" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E404" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B405" t="s">
-        <v>326</v>
+        <v>426</v>
       </c>
       <c r="C405" t="s">
-        <v>327</v>
+        <v>427</v>
       </c>
       <c r="D405" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E405" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B406" t="s">
-        <v>326</v>
+        <v>429</v>
       </c>
       <c r="C406" t="s">
-        <v>327</v>
+        <v>430</v>
       </c>
       <c r="D406" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E406" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B407" t="s">
         <v>429</v>
@@ -8687,15 +8684,15 @@
         <v>430</v>
       </c>
       <c r="D407" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E407" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B408" t="s">
         <v>429</v>
@@ -8704,15 +8701,15 @@
         <v>430</v>
       </c>
       <c r="D408" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E408" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B409" t="s">
         <v>429</v>
@@ -8721,15 +8718,15 @@
         <v>430</v>
       </c>
       <c r="D409" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E409" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B410" t="s">
         <v>429</v>
@@ -8738,15 +8735,15 @@
         <v>430</v>
       </c>
       <c r="D410" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E410" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B411" t="s">
         <v>429</v>
@@ -8755,15 +8752,15 @@
         <v>430</v>
       </c>
       <c r="D411" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E411" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B412" t="s">
         <v>429</v>
@@ -8772,32 +8769,32 @@
         <v>430</v>
       </c>
       <c r="D412" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E412" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B413" t="s">
-        <v>326</v>
+        <v>429</v>
       </c>
       <c r="C413" t="s">
-        <v>327</v>
+        <v>430</v>
       </c>
       <c r="D413" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E413" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B414" t="s">
         <v>429</v>
@@ -8806,15 +8803,15 @@
         <v>430</v>
       </c>
       <c r="D414" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E414" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B415" t="s">
         <v>429</v>
@@ -8823,15 +8820,15 @@
         <v>430</v>
       </c>
       <c r="D415" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E415" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B416" t="s">
         <v>429</v>
@@ -8840,15 +8837,15 @@
         <v>430</v>
       </c>
       <c r="D416" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E416" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B417" t="s">
         <v>429</v>
@@ -8857,15 +8854,15 @@
         <v>430</v>
       </c>
       <c r="D417" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E417" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B418" t="s">
         <v>429</v>
@@ -8874,15 +8871,15 @@
         <v>430</v>
       </c>
       <c r="D418" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E418" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B419" t="s">
         <v>429</v>
@@ -8891,15 +8888,15 @@
         <v>430</v>
       </c>
       <c r="D419" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E419" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B420" t="s">
         <v>429</v>
@@ -8908,15 +8905,15 @@
         <v>430</v>
       </c>
       <c r="D420" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E420" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B421" t="s">
         <v>429</v>
@@ -8925,15 +8922,15 @@
         <v>430</v>
       </c>
       <c r="D421" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E421" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B422" t="s">
         <v>429</v>
@@ -8942,15 +8939,15 @@
         <v>430</v>
       </c>
       <c r="D422" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E422" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B423" t="s">
         <v>429</v>
@@ -8959,15 +8956,15 @@
         <v>430</v>
       </c>
       <c r="D423" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E423" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B424" t="s">
         <v>429</v>
@@ -8976,15 +8973,15 @@
         <v>430</v>
       </c>
       <c r="D424" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E424" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B425" t="s">
         <v>429</v>
@@ -8993,32 +8990,32 @@
         <v>430</v>
       </c>
       <c r="D425" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E425" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B426" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C426" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D426" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E426" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B427" t="s">
         <v>429</v>
@@ -9027,61 +9024,27 @@
         <v>430</v>
       </c>
       <c r="D427" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E427" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B428" t="s">
-        <v>326</v>
+        <v>426</v>
       </c>
       <c r="C428" t="s">
-        <v>327</v>
+        <v>427</v>
       </c>
       <c r="D428" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="E428" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="429">
-      <c r="A429" t="s">
-        <v>476</v>
-      </c>
-      <c r="B429" t="s">
-        <v>326</v>
-      </c>
-      <c r="C429" t="s">
-        <v>327</v>
-      </c>
-      <c r="D429" t="s">
-        <v>289</v>
-      </c>
-      <c r="E429" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="430">
-      <c r="A430" t="s">
-        <v>477</v>
-      </c>
-      <c r="B430" t="s">
-        <v>227</v>
-      </c>
-      <c r="C430" t="s">
-        <v>228</v>
-      </c>
-      <c r="D430" t="s">
-        <v>197</v>
-      </c>
-      <c r="E430" t="s">
-        <v>198</v>
+        <v>293</v>
       </c>
     </row>
   </sheetData>
